--- a/excel-files/LAS PINAS/TALON VILLAGE NATIONAL HIGH SCHOOL.xlsx
+++ b/excel-files/LAS PINAS/TALON VILLAGE NATIONAL HIGH SCHOOL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29602"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29819"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="293" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{44B48D4B-ACCB-44A4-A129-A24DE771CC82}"/>
+  <xr:revisionPtr revIDLastSave="412" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CE7B234A-6099-486C-BFD1-D1449AB382B4}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBooks" sheetId="1" r:id="rId1"/>
@@ -742,6 +742,12 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -753,12 +759,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5527,8 +5527,8 @@
   </protectedRanges>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E14:E19 E21:E29 E31:E39 E51:E59 E61:E69 E41:E49 E2:E6 E71:E79 E81:E89 E8:E12 E91:E98" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E91:E98 E2:E6 E8:E12 E14:E19 E21:E29 E31:E39 E41:E49 E51:E59 E61:E69 E71:E79 E81:E89" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F21:F29 F31:F39 F41:F49 F51:F59 F61:F69 F71:F79 F81:F89 F2:F6 F8:F12 F91:F98" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
       <formula1>"CO,RO,SDO"</formula1>
@@ -5543,7 +5543,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0858F8C8-8AF8-4852-B88C-61047AF726C8}">
-  <dimension ref="A1:AA157"/>
+  <dimension ref="A1:AA127"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -5573,38 +5573,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
-      <c r="D1" s="40" t="s">
+      <c r="D1" s="42" t="s">
         <v>33</v>
       </c>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
-      <c r="J1" s="41" t="s">
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="43" t="s">
         <v>34</v>
       </c>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="41"/>
-      <c r="P1" s="42" t="s">
+      <c r="K1" s="43"/>
+      <c r="L1" s="43"/>
+      <c r="M1" s="43"/>
+      <c r="N1" s="43"/>
+      <c r="O1" s="43"/>
+      <c r="P1" s="44" t="s">
         <v>35</v>
       </c>
-      <c r="Q1" s="42"/>
-      <c r="R1" s="42"/>
-      <c r="S1" s="42"/>
-      <c r="T1" s="42"/>
-      <c r="U1" s="42"/>
-      <c r="V1" s="43" t="s">
+      <c r="Q1" s="44"/>
+      <c r="R1" s="44"/>
+      <c r="S1" s="44"/>
+      <c r="T1" s="44"/>
+      <c r="U1" s="44"/>
+      <c r="V1" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="W1" s="43"/>
-      <c r="X1" s="43"/>
-      <c r="Y1" s="43"/>
-      <c r="Z1" s="43"/>
-      <c r="AA1" s="43"/>
+      <c r="W1" s="45"/>
+      <c r="X1" s="45"/>
+      <c r="Y1" s="45"/>
+      <c r="Z1" s="45"/>
+      <c r="AA1" s="45"/>
     </row>
     <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
       <c r="A2" s="15" t="s">
@@ -5643,10 +5643,10 @@
       <c r="L2" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M2" s="44" t="s">
+      <c r="M2" s="40" t="s">
         <v>46</v>
       </c>
-      <c r="N2" s="44" t="s">
+      <c r="N2" s="40" t="s">
         <v>47</v>
       </c>
       <c r="O2" s="22" t="s">
@@ -5679,10 +5679,10 @@
       <c r="X2" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="Y2" s="45" t="s">
+      <c r="Y2" s="41" t="s">
         <v>58</v>
       </c>
-      <c r="Z2" s="45" t="s">
+      <c r="Z2" s="41" t="s">
         <v>59</v>
       </c>
       <c r="AA2" s="26" t="s">
@@ -5768,7 +5768,7 @@
       <c r="Z4" s="13"/>
       <c r="AA4" s="13"/>
     </row>
-    <row r="5" spans="1:27" ht="19.149999999999999">
+    <row r="5" spans="1:27" ht="38.25">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -6747,7 +6747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="19.149999999999999">
+    <row r="20" spans="1:27" ht="19.5">
       <c r="A20" s="1">
         <v>2</v>
       </c>
@@ -7534,7 +7534,7 @@
       <c r="Z32" s="13"/>
       <c r="AA32" s="13"/>
     </row>
-    <row r="33" spans="1:27" ht="19.149999999999999">
+    <row r="33" spans="1:27" ht="19.5">
       <c r="A33" s="1">
         <v>4</v>
       </c>
@@ -7948,7 +7948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="19.149999999999999">
+    <row r="39" spans="1:27" ht="19.5">
       <c r="A39" s="1">
         <v>4</v>
       </c>
@@ -8017,7 +8017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="19.149999999999999">
+    <row r="40" spans="1:27" ht="19.5">
       <c r="A40" s="1">
         <v>4</v>
       </c>
@@ -8238,7 +8238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="19.149999999999999">
+    <row r="44" spans="1:27" ht="19.5">
       <c r="A44" s="1">
         <v>5</v>
       </c>
@@ -8307,7 +8307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="19.149999999999999">
+    <row r="45" spans="1:27" ht="19.5">
       <c r="A45" s="1">
         <v>5</v>
       </c>
@@ -8376,7 +8376,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="19.149999999999999">
+    <row r="46" spans="1:27" ht="19.5">
       <c r="A46" s="1">
         <v>5</v>
       </c>
@@ -8445,7 +8445,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="19.149999999999999">
+    <row r="47" spans="1:27" ht="19.5">
       <c r="A47" s="1">
         <v>5</v>
       </c>
@@ -8514,7 +8514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="19.149999999999999">
+    <row r="48" spans="1:27" ht="19.5">
       <c r="A48" s="1">
         <v>5</v>
       </c>
@@ -8583,7 +8583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="19.149999999999999">
+    <row r="49" spans="1:27" ht="19.5">
       <c r="A49" s="1">
         <v>5</v>
       </c>
@@ -8652,7 +8652,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="19.149999999999999">
+    <row r="50" spans="1:27" ht="19.5">
       <c r="A50" s="1">
         <v>5</v>
       </c>
@@ -8721,7 +8721,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="19.149999999999999">
+    <row r="51" spans="1:27" ht="19.5">
       <c r="A51" s="1">
         <v>5</v>
       </c>
@@ -8804,7 +8804,7 @@
       <c r="Z52" s="13"/>
       <c r="AA52" s="13"/>
     </row>
-    <row r="53" spans="1:27" ht="19.149999999999999">
+    <row r="53" spans="1:27" ht="19.5">
       <c r="A53" s="1">
         <v>6</v>
       </c>
@@ -8873,7 +8873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:27" ht="19.149999999999999">
+    <row r="54" spans="1:27" ht="19.5">
       <c r="A54" s="1">
         <v>6</v>
       </c>
@@ -8942,7 +8942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:27" ht="19.149999999999999">
+    <row r="55" spans="1:27" ht="19.5">
       <c r="A55" s="1">
         <v>6</v>
       </c>
@@ -9011,7 +9011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:27" ht="19.149999999999999">
+    <row r="56" spans="1:27" ht="19.5">
       <c r="A56" s="1">
         <v>6</v>
       </c>
@@ -9080,7 +9080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="19.149999999999999">
+    <row r="57" spans="1:27" ht="19.5">
       <c r="A57" s="1">
         <v>6</v>
       </c>
@@ -9149,7 +9149,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="19.149999999999999">
+    <row r="58" spans="1:27" ht="19.5">
       <c r="A58" s="1">
         <v>6</v>
       </c>
@@ -9218,7 +9218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="19.149999999999999">
+    <row r="59" spans="1:27" ht="19.5">
       <c r="A59" s="1">
         <v>6</v>
       </c>
@@ -9287,7 +9287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:27" ht="19.149999999999999">
+    <row r="60" spans="1:27" ht="19.5">
       <c r="A60" s="1">
         <v>6</v>
       </c>
@@ -9356,7 +9356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:27" ht="19.149999999999999">
+    <row r="61" spans="1:27" ht="19.5">
       <c r="A61" s="1">
         <v>6</v>
       </c>
@@ -12479,7 +12479,7 @@
       <c r="Z102" s="13"/>
       <c r="AA102" s="13"/>
     </row>
-    <row r="103" spans="1:27" ht="38.450000000000003">
+    <row r="103" spans="1:27" ht="38.25">
       <c r="A103" s="1" t="s">
         <v>24</v>
       </c>
@@ -13600,7 +13600,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:27" ht="19.149999999999999">
+    <row r="121" spans="1:27" ht="19.5">
       <c r="A121" s="1"/>
       <c r="B121" s="9"/>
       <c r="C121" s="1"/>
@@ -14031,190 +14031,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:27">
-      <c r="J128" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="129" spans="10:10">
-      <c r="J129" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="130" spans="10:10">
-      <c r="J130" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="131" spans="10:10">
-      <c r="J131" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="132" spans="10:10">
-      <c r="J132" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="133" spans="10:10">
-      <c r="J133" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="134" spans="10:10">
-      <c r="J134" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="135" spans="10:10">
-      <c r="J135" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="136" spans="10:10">
-      <c r="J136" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="137" spans="10:10">
-      <c r="J137" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="138" spans="10:10">
-      <c r="J138" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="139" spans="10:10">
-      <c r="J139" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="140" spans="10:10">
-      <c r="J140" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="141" spans="10:10">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="10:10">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="10:10">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="10:10">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C3 C14:C21 C23:C31 C33:C41 C43:C51 C53:C61 C103:C110 C112:C127 C5:C12 C63:C71 C73:C81 C83:C91 C93:C101 E73:E81 E93:E101 K73:K81 K93:K101" name="Textbooks"/>
-    <protectedRange sqref="J2:L3 D2:F3 H5:L5 D14:F21 Q14:R21 W14:X21 D23:F31 Q23:R31 W23:X31 D33:F41 H33:I41 Q33:R41 W33:X41 D43:F51 H43:I51 Q43:R51 W43:X51 D53:F61 H53:I61 Q53:R61 W53:X61 H63:I71 Q63:R71 W63:X71 D73:D81 H73:I81 Q73:R81 W73:X81 H83:I91 Q83:R91 W83:X91 H93:I101 Q93:R101 W93:X101 D103:F110 H103:I110 Q103:R110 W103:X110 D112:F127 H112:I127 N127:R127 W112:X127 H14:I21 H23:I31 H6:I12 K6:L12 K33:L41 K43:L51 K53:L61 K103:L110 K112:L127 K14:L21 K23:L31 Q112:R126 P2:R2 V2:X3 N13:P126 T13:V127 J6:J127 D5:F12 N5:R12 T5:X12 N4:P4 T4:V4 J4 Z4:AA127 N3:R3 Y13 F73:F81 L73:L81 D93:D101 F93:F101 L93:L101 D63:F71 D83:F91 K63:L71 K83:L91" name="LAS"/>
+    <protectedRange sqref="J2:L3 D2:F3 H5:L5 D14:F21 Q14:R21 W14:X21 D23:F31 Q23:R31 W23:X31 D33:F41 H33:I41 Q33:R41 W33:X41 H43:I51 Q43:R51 W43:X51 H53:I61 Q53:R61 W53:X61 H63:I71 Q63:R71 W63:X71 D73:D81 H73:I81 Q73:R81 W73:X81 H83:I91 Q83:R91 W83:X91 H93:I101 Q93:R101 W93:X101 D103:F110 H103:I110 Q103:R110 W103:X110 D112:F127 H112:I127 N127:R127 W112:X127 H14:I21 H23:I31 H6:I12 K6:L12 K33:L41 K43:L51 K53:L61 K103:L110 K112:L127 K14:L21 K23:L31 Q112:R126 P2:R2 V2:X3 N13:P126 T13:V127 J6:J127 D5:F12 N5:R12 T5:X12 N4:P4 T4:V4 J4 Z4:AA127 N3:R3 Y13 F73:F81 L73:L81 D93:D101 F93:F101 L93:L101 D63:F71 D83:F91 K63:L71 K83:L91 D43:F51 D53:F61" name="LAS"/>
     <protectedRange sqref="G2:I3 M2:O2 S2:U3 Y2:AA3 G112:G127 M112:M127 S112:S127 Y112:Y127 G5:G12 M5:M12 S4:S110 Y5:Y12 G14:G21 M3 Y14:Y110 G23:G31 G33:G41 G43:G51 G53:G61 G103:G110 G63:G71 G73:G81 G83:G91 G93:G101 M14:M110" name="SOURCE"/>
   </protectedRanges>
   <dataConsolidate/>
@@ -14224,15 +14044,24 @@
     <mergeCell ref="P1:U1"/>
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
-  <dataValidations count="3">
+  <dataValidations count="6">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S112:S127 M112:M127 Y112:Y127 G112:G127" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X23:X31 X33:X41 X43:X51 X63:X71 X73:X81 X53:X61 L112:L127 X83:X91 X93:X101 X14:X21 X5:X12 L23:L31 L33:L41 L43:L51 F83:F91 L63:L71 L53:L61 R112:R127 L73:L81 F93:F101 L14:L21 L5:L12 R23:R31 R33:R41 R43:R51 R63:R71 R73:R81 R53:R61 F112:F127 R83:R91 R93:R101 R14:R21 R5:R12 F23:F31 F33:F41 F43:F51 X112:X127 F63:F71 F53:F61 F5:F12 F73:F81 L83:L91 F14:F21 F103:F110 R103:R110 L103:L110 X103:X110 L93:L101" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X112:X127" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G83:G91 Y14:Y110 S4:S110 G5:G12 M5:M12 Y5:Y12 G14:G21 G23:G31 G33:G41 G43:G51 G53:G61 G103:G110 G63:G71 G73:G81 G93:G101 M14:M110" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F5:F12 F14:F21 F23:F31 F33:F41 F43:F51 F53:F61 F63:F71 F73:F81 F83:F91 F93:F101 F103:F110 F112:F127 L5:L12 L14:L21 L23:L31 L33:L41 L43:L51 L53:L61 L63:L71 L73:L81 L83:L91 L93:L101 L103:L110 L112:L127" xr:uid="{122C2E22-8832-42EE-8A44-2B15CFE0C22E}">
+      <formula1>"2024,2025,2026"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R5:R12" xr:uid="{250D7DED-30B6-44EE-98FE-446345FD01B7}">
+      <formula1>"2024,2025,,2026"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R112:R127 R14:R21 R33:R41 R43:R51 R53:R61 R63:R71 R73:R81 R83:R91 R93:R101 R103:R110 R23:R31 X5:X12 X14:X21 X23:X31 X33:X41 X43:X51 X53:X61 X63:X71 X73:X81 X83:X91 X93:X101 X103:X110" xr:uid="{60BD1842-62BD-4D53-971D-EEC5DD030B16}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14277,38 +14106,38 @@
   <sheetData>
     <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
       <c r="B1" s="35"/>
-      <c r="D1" s="40" t="s">
+      <c r="D1" s="42" t="s">
         <v>33</v>
       </c>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
-      <c r="J1" s="41" t="s">
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="43" t="s">
         <v>34</v>
       </c>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="41"/>
-      <c r="P1" s="42" t="s">
+      <c r="K1" s="43"/>
+      <c r="L1" s="43"/>
+      <c r="M1" s="43"/>
+      <c r="N1" s="43"/>
+      <c r="O1" s="43"/>
+      <c r="P1" s="44" t="s">
         <v>35</v>
       </c>
-      <c r="Q1" s="42"/>
-      <c r="R1" s="42"/>
-      <c r="S1" s="42"/>
-      <c r="T1" s="42"/>
-      <c r="U1" s="42"/>
-      <c r="V1" s="43" t="s">
+      <c r="Q1" s="44"/>
+      <c r="R1" s="44"/>
+      <c r="S1" s="44"/>
+      <c r="T1" s="44"/>
+      <c r="U1" s="44"/>
+      <c r="V1" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="W1" s="43"/>
-      <c r="X1" s="43"/>
-      <c r="Y1" s="43"/>
-      <c r="Z1" s="43"/>
-      <c r="AA1" s="43"/>
+      <c r="W1" s="45"/>
+      <c r="X1" s="45"/>
+      <c r="Y1" s="45"/>
+      <c r="Z1" s="45"/>
+      <c r="AA1" s="45"/>
     </row>
     <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
       <c r="A2" s="15" t="s">
@@ -14347,10 +14176,10 @@
       <c r="L2" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="M2" s="44" t="s">
+      <c r="M2" s="40" t="s">
         <v>73</v>
       </c>
-      <c r="N2" s="44" t="s">
+      <c r="N2" s="40" t="s">
         <v>74</v>
       </c>
       <c r="O2" s="22" t="s">
@@ -14383,17 +14212,17 @@
       <c r="X2" s="27" t="s">
         <v>84</v>
       </c>
-      <c r="Y2" s="45" t="s">
+      <c r="Y2" s="41" t="s">
         <v>85</v>
       </c>
-      <c r="Z2" s="45" t="s">
+      <c r="Z2" s="41" t="s">
         <v>86</v>
       </c>
       <c r="AA2" s="26" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="19.149999999999999">
+    <row r="3" spans="1:27" ht="19.5">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -14462,7 +14291,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="19.149999999999999">
+    <row r="4" spans="1:27" ht="19.5">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -15084,7 +14913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="19.149999999999999">
+    <row r="14" spans="1:27" ht="19.5">
       <c r="A14" s="1">
         <v>2</v>
       </c>
@@ -16466,7 +16295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="19.149999999999999">
+    <row r="36" spans="1:27" ht="19.5">
       <c r="A36" s="1">
         <v>4</v>
       </c>
@@ -16881,7 +16710,7 @@
       </c>
     </row>
     <row r="42" spans="1:27" s="7" customFormat="1"/>
-    <row r="43" spans="1:27" ht="19.149999999999999">
+    <row r="43" spans="1:27" ht="19.5">
       <c r="A43" s="1">
         <v>5</v>
       </c>
@@ -23086,12 +22915,18 @@
     <mergeCell ref="P1:U1"/>
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
-  <dataValidations count="2">
+  <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S115:S122 Y115:Y122 G115:G122 Y3:Y10 S3:S10 M3:M10 G3:G10 G12:G19 Y12:Y19 S12:S19 M12:M19 M21:M29 G21:G29 Y21:Y29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 G55:G65 Y55:Y65 S55:S65 M55:M65 M67:M77 G67:G77 Y67:Y77 S67:S77 S79:S89 M79:M89 M103:M113 Y79:Y89 Y103:Y113 Y91:Y101 G103:G113 M115:M122 S91:S101 S103:S113 G79:G89 M91:M101 G91:G101" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X21:X29 X31:X41 X43:X53 X67:X77 X79:X89 X55:X65 X103:X113 R103:R113 X12:X19 X3:X10 L21:L29 L31:L41 L43:L53 L67:L77 L79:L89 L55:L65 F103:F113 L91:L101 L12:L19 L3:L10 R21:R29 R31:R41 R43:R53 R67:R77 R79:R89 R55:R65 X91:X101 F79:F89 R12:R19 R3:R10 F21:F29 F31:F41 F43:F53 F67:F77 L103:L113 F55:F65 F3:F10 R91:R101 X115:X122 F12:F19 F115:F122 R115:R122 L115:L122 F91:F101" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X115:X122" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
+      <formula1>"2024,2025,2026"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F10 F12:F19 F21:F29 F31:F41 F43:F53 F55:F65 F67:F77 F79:F89 F91:F101 F103:F113 F115:F122 L3:L10 L12:L19 L21:L29 L31:L41 L43:L53 L55:L65 L67:L77 L79:L89 L91:L101 L103:L113 L115:L122 R3:R10 R12:R19 R21:R29 R31:R41 R43:R53 R55:R65 R67:R77 R79:R89 R91:R101 R103:R113 R115:R122 X3:X10 X21:X29 X31:X41 X43:X53 X55:X65 X67:X77 X79:X89 X91:X101 X103:X113" xr:uid="{4F14ABFA-BFC5-4C7A-8A2B-4AD174B73588}">
+      <formula1>"2024,2025,2026"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X12:X19" xr:uid="{6B720B5A-9745-441B-9D49-3CE3294AA183}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
